--- a/data/trending_integrated_20260917_15.xlsx
+++ b/data/trending_integrated_20260917_15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4630</v>
+        <v>4617</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.57%</t>
+          <t>'+20.23%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>669</v>
+        <v>689</v>
       </c>
       <c r="F2" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G2" t="n">
-        <v>1636</v>
+        <v>1666</v>
       </c>
       <c r="H2" t="n">
         <v>0.95</v>
@@ -610,7 +610,7 @@
         <v>1.03</v>
       </c>
       <c r="O2" t="n">
-        <v>308173862351</v>
+        <v>312562107417</v>
       </c>
       <c r="P2" t="n">
         <v>6900</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1684</v>
+        <v>1672</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.54%</t>
+          <t>'+19.69%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H3" t="n">
         <v>3.52</v>
@@ -702,7 +702,7 @@
         <v>3.57</v>
       </c>
       <c r="O3" t="n">
-        <v>54860426635</v>
+        <v>55411295604</v>
       </c>
       <c r="P3" t="n">
         <v>5140</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21350</v>
+        <v>21400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.03%</t>
+          <t>'+15.30%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G4" t="n">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="H4" t="n">
         <v>2.54</v>
@@ -794,7 +794,7 @@
         <v>1.92</v>
       </c>
       <c r="O4" t="n">
-        <v>297718012870</v>
+        <v>299803399320</v>
       </c>
       <c r="P4" t="n">
         <v>59600</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3840</v>
+        <v>3845</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.71%</t>
+          <t>'+9.86%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="H5" t="n">
         <v>8.01</v>
@@ -886,7 +886,7 @@
         <v>8.06</v>
       </c>
       <c r="O5" t="n">
-        <v>98406539533</v>
+        <v>98885990735</v>
       </c>
       <c r="P5" t="n">
         <v>19950</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>스페이스X 관련주로 부각되며 상승 시도. 프로그램 매수세 및 기관 순매수 관찰.</t>
+          <t>스페이스X 관련주로 부각. 거래량 및 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['스페이스X', '우주항공주', '프로그램매수']</t>
+          <t>['스페이스X', '거래량', '주가상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21400</v>
+        <v>21450</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.94%</t>
+          <t>'+6.19%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.15</v>
       </c>
       <c r="E6" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F6" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H6" t="n">
         <v>28.36</v>
@@ -978,7 +978,7 @@
         <v>28.51</v>
       </c>
       <c r="O6" t="n">
-        <v>85825799725</v>
+        <v>87462904150</v>
       </c>
       <c r="P6" t="n">
         <v>35350</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10400</v>
+        <v>10455</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.31%</t>
+          <t>'+4.86%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.58</v>
       </c>
       <c r="E7" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F7" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" t="n">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="H7" t="n">
         <v>1.25</v>
@@ -1070,7 +1070,7 @@
         <v>0.67</v>
       </c>
       <c r="O7" t="n">
-        <v>179387449785</v>
+        <v>180016907540</v>
       </c>
       <c r="P7" t="n">
         <v>15960</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모치료제 관련 호재 기대감과 외인 매도세 관찰.</t>
+          <t>낙태약 및 탈모 치료제 관련 기대감. 예상 매출 1조 이상 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료제', '외인매도']</t>
+          <t>['낙태약', '탈모치료', '매출']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13330</v>
+        <v>13310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.17%</t>
+          <t>'+3.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.13</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="H8" t="n">
         <v>4.99</v>
@@ -1162,7 +1162,7 @@
         <v>5.12</v>
       </c>
       <c r="O8" t="n">
-        <v>61808854070</v>
+        <v>62748721345</v>
       </c>
       <c r="P8" t="n">
         <v>30200</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85200</v>
+        <v>85300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.67%</t>
+          <t>'+1.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.1</v>
       </c>
       <c r="E9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F9" t="n">
         <v>129</v>
       </c>
       <c r="G9" t="n">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="H9" t="n">
         <v>23.27</v>
@@ -1254,7 +1254,7 @@
         <v>23.37</v>
       </c>
       <c r="O9" t="n">
-        <v>126956026850</v>
+        <v>130405839150</v>
       </c>
       <c r="P9" t="n">
         <v>139200</v>
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16010</v>
+        <v>11650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.56%</t>
+          <t>'+0.17%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.93</v>
+        <v>0.3</v>
       </c>
       <c r="E10" t="n">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="F10" t="n">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="G10" t="n">
-        <v>1417</v>
+        <v>437</v>
       </c>
       <c r="H10" t="n">
-        <v>4.88</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>16100</v>
+        <v>11630</v>
       </c>
       <c r="K10" t="n">
-        <v>16200</v>
+        <v>11700</v>
       </c>
       <c r="L10" t="n">
-        <v>16750</v>
+        <v>12760</v>
       </c>
       <c r="M10" t="n">
-        <v>15560</v>
+        <v>11500</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>8.4</v>
       </c>
       <c r="O10" t="n">
-        <v>351602889395</v>
+        <v>49063950770</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>21150</v>
       </c>
       <c r="Q10" t="n">
-        <v>1272</v>
+        <v>8140</v>
       </c>
       <c r="R10" t="n">
-        <v>-686000</v>
+        <v>261000</v>
       </c>
       <c r="S10" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 호재에 따른 주가 상승 기대. 외인 대규모 매수 관찰.</t>
+          <t>주가 사기 의혹 및 삼성 인수 루머에 대한 비판. 목표 주가 25000원 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['광통신', '미국수주', '외인매수']</t>
+          <t>['주가사기', '삼성인수', '목표주가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252000</v>
+        <v>252750</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-0.30%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="G11" t="n">
-        <v>1751</v>
+        <v>1782</v>
       </c>
       <c r="H11" t="n">
         <v>46.52</v>
@@ -1438,7 +1438,7 @@
         <v>46.56</v>
       </c>
       <c r="O11" t="n">
-        <v>2355576723500</v>
+        <v>2425957877250</v>
       </c>
       <c r="P11" t="n">
         <v>374500</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 논쟁으로 인한 종목 관련 게시글의 신뢰도 저하. 객관적 분석이나 팩트 부재.</t>
+          <t>정치적 성향 관련 논쟁 및 정치인 관련 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치', '대선', '주가조작']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,123 +1483,123 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18410</v>
+        <v>16040</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.86%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.21</v>
+        <v>2.93</v>
       </c>
       <c r="E12" t="n">
-        <v>107</v>
+        <v>262</v>
       </c>
       <c r="F12" t="n">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="G12" t="n">
-        <v>395</v>
+        <v>1422</v>
       </c>
       <c r="H12" t="n">
-        <v>10.85</v>
+        <v>4.88</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18570</v>
+        <v>16100</v>
       </c>
       <c r="K12" t="n">
-        <v>18740</v>
+        <v>16200</v>
       </c>
       <c r="L12" t="n">
-        <v>18900</v>
+        <v>16750</v>
       </c>
       <c r="M12" t="n">
-        <v>18350</v>
+        <v>15560</v>
       </c>
       <c r="N12" t="n">
-        <v>10.64</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>60453779135</v>
+        <v>353131684835</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R12" t="n">
-        <v>-306000</v>
+        <v>-686000</v>
       </c>
       <c r="S12" t="n">
-        <v>-77000</v>
+        <v>4000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
+          <t>미국 광통신 시장 호재에 따른 주가 상승 기대. 외인 대규모 매수 관찰.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['대규모계약', 'LNG', '대차해지']</t>
+          <t>['광통신', '미국수주', '외인매수']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8390</v>
+        <v>18450</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-0.65%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.12</v>
+        <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
-        <v>371</v>
+        <v>406</v>
       </c>
       <c r="H13" t="n">
-        <v>26.54</v>
+        <v>10.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,60 +1607,60 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8470</v>
+        <v>18570</v>
       </c>
       <c r="K13" t="n">
-        <v>8470</v>
+        <v>18740</v>
       </c>
       <c r="L13" t="n">
-        <v>8510</v>
+        <v>18900</v>
       </c>
       <c r="M13" t="n">
-        <v>8360</v>
+        <v>18350</v>
       </c>
       <c r="N13" t="n">
-        <v>26.66</v>
+        <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>15019976615</v>
+        <v>61791039755</v>
       </c>
       <c r="P13" t="n">
-        <v>17950</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>8120</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-236000</v>
+        <v>-306000</v>
       </c>
       <c r="S13" t="n">
-        <v>-5000</v>
+        <v>-77000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>4분기 전망 및 중국 경쟁 심화 우려. 무능한 경영진과 높은 부채 비중, 목표가 하향 조정 등 악재 지속.</t>
+          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['부채', '경쟁력', '목표가']</t>
+          <t>['대규모계약', 'LNG', '대차해지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1742000</v>
+        <v>1746000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.97%</t>
+          <t>'-0.74%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G14" t="n">
-        <v>1695</v>
+        <v>1701</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>3985651175500</v>
+        <v>4071780314000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 시즌 진입 및 금리 인상 수혜 기대감 속 홀딩 권유. 단기적 등락 가능성 및 투자 주체별 전략 필요.</t>
+          <t>홀딩 및 실적 시즌 대비. 금리 인상 수혜 및 200돌파 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '금리인상']</t>
+          <t>['실적시즌', '금리인상', '주가상승']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,123 +1759,123 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3460</v>
+        <v>8370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.85</v>
+        <v>-0.12</v>
       </c>
       <c r="E15" t="n">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G15" t="n">
-        <v>322</v>
+        <v>381</v>
       </c>
       <c r="H15" t="n">
-        <v>2.26</v>
+        <v>26.54</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3520</v>
+        <v>8470</v>
       </c>
       <c r="K15" t="n">
-        <v>3730</v>
+        <v>8470</v>
       </c>
       <c r="L15" t="n">
-        <v>3750</v>
+        <v>8510</v>
       </c>
       <c r="M15" t="n">
-        <v>3420</v>
+        <v>8350</v>
       </c>
       <c r="N15" t="n">
-        <v>3.11</v>
+        <v>26.66</v>
       </c>
       <c r="O15" t="n">
-        <v>6071176218</v>
+        <v>16678589730</v>
       </c>
       <c r="P15" t="n">
-        <v>16110</v>
+        <v>17950</v>
       </c>
       <c r="Q15" t="n">
-        <v>2300</v>
+        <v>8120</v>
       </c>
       <c r="R15" t="n">
-        <v>-328000</v>
+        <v>-236000</v>
       </c>
       <c r="S15" t="n">
-        <v>-9000</v>
+        <v>-5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
+          <t>4분기 전망 및 중국 경쟁 심화 우려. 무능한 경영진과 높은 부채 비중, 목표가 하향 조정 등 악재 지속.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['상장폐지', '폭락', '차익실현']</t>
+          <t>['부채', '경쟁력', '목표가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>55</v>
+        <v>3460</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.79%</t>
+          <t>'-1.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="E16" t="n">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>267</v>
+        <v>323</v>
       </c>
       <c r="H16" t="n">
-        <v>3.71</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,71 +1883,71 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>56</v>
+        <v>3520</v>
       </c>
       <c r="K16" t="n">
-        <v>56</v>
+        <v>3730</v>
       </c>
       <c r="L16" t="n">
-        <v>90</v>
+        <v>3750</v>
       </c>
       <c r="M16" t="n">
-        <v>55</v>
+        <v>3420</v>
       </c>
       <c r="N16" t="n">
-        <v>3.71</v>
+        <v>3.11</v>
       </c>
       <c r="O16" t="n">
-        <v>634666899</v>
+        <v>6202100725</v>
       </c>
       <c r="P16" t="n">
-        <v>901</v>
+        <v>16110</v>
       </c>
       <c r="Q16" t="n">
-        <v>55</v>
+        <v>2300</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-328000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>방산용 AR 디스플레이 양산 협력 등 신사업 본격화. 차익 실현 및 단기 급등 가능성, 투자 주의 요구.</t>
+          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AR디스플레이', '신사업']</t>
+          <t>['상장폐지', '폭락', '차익실현']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>원풍물산</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13720</v>
+        <v>55</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1955,19 +1955,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F17" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>395</v>
+        <v>281</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>3.71</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13970</v>
+        <v>56</v>
       </c>
       <c r="K17" t="n">
-        <v>13450</v>
+        <v>56</v>
       </c>
       <c r="L17" t="n">
-        <v>13970</v>
+        <v>90</v>
       </c>
       <c r="M17" t="n">
-        <v>13410</v>
+        <v>55</v>
       </c>
       <c r="N17" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O17" t="n">
+        <v>634666899</v>
+      </c>
+      <c r="P17" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>55</v>
+      </c>
+      <c r="R17" t="n">
         <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>16504634800</v>
-      </c>
-      <c r="P17" t="n">
-        <v>36200</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>8920</v>
-      </c>
-      <c r="R17" t="n">
-        <v>122000</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유가 변동성 및 지정학적 리스크에 따른 주가 등락. 외국인 매수세와 프로그램 매도 공존.</t>
+          <t>미 선다이오드와 방산용 AR 디스플레이 양산 협력. 신사업 본격화.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유가', '지정학적 리스크', '외국인']</t>
+          <t>['AR디스플레이', '방산', '신사업']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>008290</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13210</v>
+        <v>13250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.37%</t>
+          <t>'-2.07%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1.36</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
         <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H18" t="n">
         <v>1.76</v>
@@ -2082,7 +2082,7 @@
         <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>83717121350</v>
+        <v>83906342190</v>
       </c>
       <c r="P18" t="n">
         <v>25700</v>
@@ -2127,162 +2127,162 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10160</v>
+        <v>13670</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.87%</t>
+          <t>'-2.15%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.8</v>
+        <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="F19" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="G19" t="n">
-        <v>142</v>
+        <v>400</v>
       </c>
       <c r="H19" t="n">
-        <v>18.42</v>
+        <v>0.01</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>10460</v>
+        <v>13970</v>
       </c>
       <c r="K19" t="n">
-        <v>10860</v>
+        <v>13450</v>
       </c>
       <c r="L19" t="n">
-        <v>11150</v>
+        <v>13970</v>
       </c>
       <c r="M19" t="n">
-        <v>10060</v>
+        <v>13410</v>
       </c>
       <c r="N19" t="n">
-        <v>19.22</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60186462390</v>
+        <v>16896844300</v>
       </c>
       <c r="P19" t="n">
-        <v>22450</v>
+        <v>36200</v>
       </c>
       <c r="Q19" t="n">
-        <v>1760</v>
+        <v>8920</v>
       </c>
       <c r="R19" t="n">
-        <v>-70000</v>
+        <v>122000</v>
       </c>
       <c r="S19" t="n">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+          <t>유가 변동성 및 지정학적 리스크에 따른 주가 등락. 외국인 매수세와 프로그램 매도 공존.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주포', '시총', '횡보']</t>
+          <t>['유가', '지정학적 리스크', '외국인']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4105</v>
+        <v>10170</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.92%</t>
+          <t>'-2.77%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.13</v>
+        <v>-0.8</v>
       </c>
       <c r="E20" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="G20" t="n">
-        <v>236</v>
+        <v>146</v>
       </c>
       <c r="H20" t="n">
-        <v>0.87</v>
+        <v>18.42</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>4410</v>
+        <v>10460</v>
       </c>
       <c r="K20" t="n">
-        <v>4415</v>
+        <v>10860</v>
       </c>
       <c r="L20" t="n">
-        <v>4420</v>
+        <v>11150</v>
       </c>
       <c r="M20" t="n">
-        <v>4025</v>
+        <v>10060</v>
       </c>
       <c r="N20" t="n">
-        <v>0.74</v>
+        <v>19.22</v>
       </c>
       <c r="O20" t="n">
-        <v>52690459217</v>
+        <v>60538682415</v>
       </c>
       <c r="P20" t="n">
-        <v>8100</v>
+        <v>22450</v>
       </c>
       <c r="Q20" t="n">
-        <v>592</v>
+        <v>1760</v>
       </c>
       <c r="R20" t="n">
-        <v>-162000</v>
+        <v>-70000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>투기 과열 종목 지정으로 인한 주가 변동성 및 매도 압력 발생. 광통신 테마 내에서 대한광통신 대비 약세 언급.</t>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,18 +2291,110 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>['주포', '시총', '횡보']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>017900</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4100</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>'-7.03%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" t="n">
+        <v>60</v>
+      </c>
+      <c r="G21" t="n">
+        <v>236</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>4410</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4415</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4420</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4025</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O21" t="n">
+        <v>53219087104</v>
+      </c>
+      <c r="P21" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>592</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-162000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>투기 과열 종목 지정으로 인한 주가 변동성 및 매도 압력 발생. 광통신 테마 내에서 대한광통신 대비 약세 언급.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
           <t>['투기과열', '광통신', '주가변동']</t>
         </is>
       </c>
-      <c r="X20" t="n">
+      <c r="X21" t="n">
         <v>8</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>추적</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>069540</t>
         </is>

--- a/data/trending_integrated_20260917_15.xlsx
+++ b/data/trending_integrated_20260917_15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>한켐</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4617</v>
+        <v>12640</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+20.23%</t>
+          <t>'+29.91%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.08</v>
+        <v>0.52</v>
       </c>
       <c r="E2" t="n">
-        <v>689</v>
+        <v>120</v>
       </c>
       <c r="F2" t="n">
-        <v>273</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>1666</v>
+        <v>157</v>
       </c>
       <c r="H2" t="n">
-        <v>0.95</v>
+        <v>1.39</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3840</v>
+        <v>9730</v>
       </c>
       <c r="K2" t="n">
-        <v>4170</v>
+        <v>9700</v>
       </c>
       <c r="L2" t="n">
-        <v>4800</v>
+        <v>12640</v>
       </c>
       <c r="M2" t="n">
-        <v>3990</v>
+        <v>9350</v>
       </c>
       <c r="N2" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="O2" t="n">
-        <v>312562107417</v>
+        <v>160218257075</v>
       </c>
       <c r="P2" t="n">
-        <v>6900</v>
+        <v>17040</v>
       </c>
       <c r="Q2" t="n">
-        <v>1738</v>
+        <v>5460</v>
       </c>
       <c r="R2" t="n">
-        <v>-138000</v>
+        <v>-12000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>카카오, 소프트뱅크 등 대형사 인수 가능성 및 10배 상승 기대감. 역사적 거래량 발생.</t>
+          <t>삼성전기 MLCC 소재 공급 확대 논의 관련 뉴스 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
+          <t>['MLCC', '소재']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>457370</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>센서뷰</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1672</v>
+        <v>4635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.69%</t>
+          <t>'+20.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>699</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>280</v>
       </c>
       <c r="G3" t="n">
-        <v>192</v>
+        <v>1702</v>
       </c>
       <c r="H3" t="n">
-        <v>3.52</v>
+        <v>0.95</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,91 +687,91 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1397</v>
+        <v>3840</v>
       </c>
       <c r="K3" t="n">
-        <v>1395</v>
+        <v>4170</v>
       </c>
       <c r="L3" t="n">
-        <v>1800</v>
+        <v>4800</v>
       </c>
       <c r="M3" t="n">
-        <v>1369</v>
+        <v>3990</v>
       </c>
       <c r="N3" t="n">
-        <v>3.57</v>
+        <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>55411295604</v>
+        <v>317849381964</v>
       </c>
       <c r="P3" t="n">
-        <v>5140</v>
+        <v>6900</v>
       </c>
       <c r="Q3" t="n">
-        <v>870</v>
+        <v>1738</v>
       </c>
       <c r="R3" t="n">
-        <v>-58000</v>
+        <v>-138000</v>
       </c>
       <c r="S3" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
+          <t>카카오 인수 및 소프트뱅크 투자 관련 루머로 급등 기대감 형성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['우주', '스페이스X', '유상증자']</t>
+          <t>['카카오 인수', '손정의']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>321370</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>센서뷰</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21400</v>
+        <v>1677</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.30%</t>
+          <t>'+20.04%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>279</v>
+        <v>196</v>
       </c>
       <c r="H4" t="n">
-        <v>2.54</v>
+        <v>3.52</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>18560</v>
+        <v>1397</v>
       </c>
       <c r="K4" t="n">
-        <v>19260</v>
+        <v>1395</v>
       </c>
       <c r="L4" t="n">
-        <v>22950</v>
+        <v>1800</v>
       </c>
       <c r="M4" t="n">
-        <v>18920</v>
+        <v>1369</v>
       </c>
       <c r="N4" t="n">
-        <v>1.92</v>
+        <v>3.57</v>
       </c>
       <c r="O4" t="n">
-        <v>299803399320</v>
+        <v>55822092167</v>
       </c>
       <c r="P4" t="n">
-        <v>59600</v>
+        <v>5140</v>
       </c>
       <c r="Q4" t="n">
-        <v>1030</v>
+        <v>870</v>
       </c>
       <c r="R4" t="n">
-        <v>-81000</v>
+        <v>-58000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2000</v>
+        <v>-7000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
+          <t>우주·방산·통신주 성장 기대감 및 스페이스X 연관성 언급. 유상증자 성공.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['CPO', '수주 공시']</t>
+          <t>['우주', '스페이스X', '유상증자']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>043260</t>
+          <t>321370</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>아주IB투자</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3845</v>
+        <v>21500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.86%</t>
+          <t>'+15.84%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>164</v>
+        <v>104</v>
       </c>
       <c r="F5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>317</v>
+        <v>279</v>
       </c>
       <c r="H5" t="n">
-        <v>8.01</v>
+        <v>2.54</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3500</v>
+        <v>18560</v>
       </c>
       <c r="K5" t="n">
-        <v>3590</v>
+        <v>19260</v>
       </c>
       <c r="L5" t="n">
-        <v>4130</v>
+        <v>22950</v>
       </c>
       <c r="M5" t="n">
-        <v>3550</v>
+        <v>18920</v>
       </c>
       <c r="N5" t="n">
-        <v>8.06</v>
+        <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>98885990735</v>
+        <v>302120369270</v>
       </c>
       <c r="P5" t="n">
-        <v>19950</v>
+        <v>59600</v>
       </c>
       <c r="Q5" t="n">
-        <v>1913</v>
+        <v>1030</v>
       </c>
       <c r="R5" t="n">
-        <v>-382000</v>
+        <v>-81000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>스페이스X 관련주로 부각. 거래량 및 주가 상승 기대감.</t>
+          <t>자회사 ADS테크 편입 및 CPO 생산장비 수주 공시 기반 AI 인프라 사업 확장 및 미국 시장 확대 전망. 광통신주 대장 역할.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['스페이스X', '거래량', '주가상승']</t>
+          <t>['CPO', '수주 공시']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,95 +919,95 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>027360</t>
+          <t>043260</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아주IB투자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21450</v>
+        <v>3845</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.19%</t>
+          <t>'+9.86%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="F6" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G6" t="n">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="H6" t="n">
-        <v>28.36</v>
+        <v>8.01</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>20200</v>
+        <v>3500</v>
       </c>
       <c r="K6" t="n">
-        <v>20450</v>
+        <v>3590</v>
       </c>
       <c r="L6" t="n">
-        <v>21800</v>
+        <v>4130</v>
       </c>
       <c r="M6" t="n">
-        <v>20450</v>
+        <v>3550</v>
       </c>
       <c r="N6" t="n">
-        <v>28.51</v>
+        <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>87462904150</v>
+        <v>100360006054</v>
       </c>
       <c r="P6" t="n">
-        <v>35350</v>
+        <v>19950</v>
       </c>
       <c r="Q6" t="n">
-        <v>18440</v>
+        <v>1913</v>
       </c>
       <c r="R6" t="n">
-        <v>1852000</v>
+        <v>-382000</v>
       </c>
       <c r="S6" t="n">
-        <v>227000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>나스닥 반등, 공매도 세력과의 수급 싸움, 수주 기대감에 따른 단기 상승 전망. 다만, 변동성 고려 필요.</t>
+          <t>스페이스X 관련주 부각 및 프로그램 매수세 유입으로 급등 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['나스닥', '공매도', '수주']</t>
+          <t>['스페이스X', '매집봉']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>027360</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10455</v>
+        <v>21500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.86%</t>
+          <t>'+6.44%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.58</v>
+        <v>-0.15</v>
       </c>
       <c r="E7" t="n">
         <v>148</v>
       </c>
       <c r="F7" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G7" t="n">
-        <v>251</v>
+        <v>373</v>
       </c>
       <c r="H7" t="n">
-        <v>1.25</v>
+        <v>28.36</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9970</v>
+        <v>20200</v>
       </c>
       <c r="K7" t="n">
-        <v>10280</v>
+        <v>20450</v>
       </c>
       <c r="L7" t="n">
-        <v>11750</v>
+        <v>21800</v>
       </c>
       <c r="M7" t="n">
-        <v>10250</v>
+        <v>20450</v>
       </c>
       <c r="N7" t="n">
-        <v>0.67</v>
+        <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>180016907540</v>
+        <v>88713161050</v>
       </c>
       <c r="P7" t="n">
-        <v>15960</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>3500</v>
+        <v>18440</v>
       </c>
       <c r="R7" t="n">
-        <v>-26000</v>
+        <v>1852000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>227000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료제 관련 기대감. 예상 매출 1조 이상 언급.</t>
+          <t>신규 수주 기대감 속 개인 투자자들의 매수세 집중.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '매출']</t>
+          <t>['신규 수주', '추세 전환']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,222 +1108,222 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13310</v>
+        <v>10460</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.02%</t>
+          <t>'+4.91%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.13</v>
+        <v>0.58</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="G8" t="n">
-        <v>490</v>
+        <v>252</v>
       </c>
       <c r="H8" t="n">
-        <v>4.99</v>
+        <v>1.25</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12920</v>
+        <v>9970</v>
       </c>
       <c r="K8" t="n">
-        <v>12920</v>
+        <v>10280</v>
       </c>
       <c r="L8" t="n">
-        <v>13770</v>
+        <v>11750</v>
       </c>
       <c r="M8" t="n">
-        <v>12910</v>
+        <v>10250</v>
       </c>
       <c r="N8" t="n">
-        <v>5.12</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>62748721345</v>
+        <v>180898787585</v>
       </c>
       <c r="P8" t="n">
-        <v>30200</v>
+        <v>15960</v>
       </c>
       <c r="Q8" t="n">
-        <v>3540</v>
+        <v>3500</v>
       </c>
       <c r="R8" t="n">
-        <v>-100000</v>
+        <v>-26000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>신한울 3.4호기 DCS 계약 체결 공시 기반 상승 기대감. 해외 원전 관련 우상향 추세.</t>
+          <t>낙태약 및 탈모 치료제 관련 기대감. 예상 매출 1조 이상 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['DCS계약', '원전', '추세']</t>
+          <t>['낙태약', '탈모치료', '매출']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85300</v>
+        <v>13330</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.79%</t>
+          <t>'+3.17%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="E9" t="n">
-        <v>211</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>799</v>
+        <v>492</v>
       </c>
       <c r="H9" t="n">
-        <v>23.27</v>
+        <v>4.99</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>83800</v>
+        <v>12920</v>
       </c>
       <c r="K9" t="n">
-        <v>84700</v>
+        <v>12920</v>
       </c>
       <c r="L9" t="n">
-        <v>86600</v>
+        <v>13770</v>
       </c>
       <c r="M9" t="n">
-        <v>84100</v>
+        <v>12910</v>
       </c>
       <c r="N9" t="n">
-        <v>23.37</v>
+        <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>130405839150</v>
+        <v>63395792040</v>
       </c>
       <c r="P9" t="n">
-        <v>139200</v>
+        <v>30200</v>
       </c>
       <c r="Q9" t="n">
-        <v>57000</v>
+        <v>3540</v>
       </c>
       <c r="R9" t="n">
-        <v>-95000</v>
+        <v>-100000</v>
       </c>
       <c r="S9" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 산업 성장 및 전력 수요 증가 전망에 따른 원전 관련주 부각. 대미 투자 및 금리 인상 변수 언급.</t>
+          <t>신한울 3.4호기 DCS 계약 체결 공시 기반 상승 기대감. 해외 원전 관련 우상향 추세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['원전', 'AI', '금리인상']</t>
+          <t>['DCS계약', '원전', '추세']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11650</v>
+        <v>85400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.17%</t>
+          <t>'+1.91%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>127</v>
+        <v>212</v>
       </c>
       <c r="F10" t="n">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="G10" t="n">
-        <v>437</v>
+        <v>802</v>
       </c>
       <c r="H10" t="n">
-        <v>8.699999999999999</v>
+        <v>23.27</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>11630</v>
+        <v>83800</v>
       </c>
       <c r="K10" t="n">
-        <v>11700</v>
+        <v>84700</v>
       </c>
       <c r="L10" t="n">
-        <v>12760</v>
+        <v>86600</v>
       </c>
       <c r="M10" t="n">
-        <v>11500</v>
+        <v>84100</v>
       </c>
       <c r="N10" t="n">
-        <v>8.4</v>
+        <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>49063950770</v>
+        <v>133569472700</v>
       </c>
       <c r="P10" t="n">
-        <v>21150</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>8140</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>261000</v>
+        <v>-95000</v>
       </c>
       <c r="S10" t="n">
-        <v>5000</v>
+        <v>44000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>주가 사기 의혹 및 삼성 인수 루머에 대한 비판. 목표 주가 25000원 언급.</t>
+          <t>미국 금리 인상 및 대미 투자 관련 논의, 원전 섹터 동반 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가사기', '삼성인수', '목표주가']</t>
+          <t>['원전', '금리 인상']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252750</v>
+        <v>16110</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.30%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>266</v>
       </c>
       <c r="F11" t="n">
-        <v>440</v>
+        <v>145</v>
       </c>
       <c r="G11" t="n">
-        <v>1782</v>
+        <v>1439</v>
       </c>
       <c r="H11" t="n">
-        <v>46.52</v>
+        <v>4.88</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>253500</v>
+        <v>16100</v>
       </c>
       <c r="K11" t="n">
-        <v>257000</v>
+        <v>16200</v>
       </c>
       <c r="L11" t="n">
-        <v>259000</v>
+        <v>16750</v>
       </c>
       <c r="M11" t="n">
-        <v>251500</v>
+        <v>15560</v>
       </c>
       <c r="N11" t="n">
-        <v>46.56</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2425957877250</v>
+        <v>355661250360</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>77100</v>
+        <v>1272</v>
       </c>
       <c r="R11" t="n">
-        <v>-718000</v>
+        <v>-686000</v>
       </c>
       <c r="S11" t="n">
-        <v>-59000</v>
+        <v>4000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 성향 관련 논쟁 및 정치인 관련 언급.</t>
+          <t>미국 광통신주 급등에 따른 국내 광통신 섹터 상승 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치', '대선', '주가조작']</t>
+          <t>['광통신', '수주']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16040</v>
+        <v>253000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.37%</t>
+          <t>'-0.20%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.93</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>262</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>142</v>
+        <v>439</v>
       </c>
       <c r="G12" t="n">
-        <v>1422</v>
+        <v>1785</v>
       </c>
       <c r="H12" t="n">
-        <v>4.88</v>
+        <v>46.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16100</v>
+        <v>253500</v>
       </c>
       <c r="K12" t="n">
-        <v>16200</v>
+        <v>257000</v>
       </c>
       <c r="L12" t="n">
-        <v>16750</v>
+        <v>259000</v>
       </c>
       <c r="M12" t="n">
-        <v>15560</v>
+        <v>251500</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>46.56</v>
       </c>
       <c r="O12" t="n">
-        <v>353131684835</v>
+        <v>2490607149250</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>77100</v>
       </c>
       <c r="R12" t="n">
-        <v>-686000</v>
+        <v>-718000</v>
       </c>
       <c r="S12" t="n">
-        <v>4000</v>
+        <v>-59000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 호재에 따른 주가 상승 기대. 외인 대규모 매수 관찰.</t>
+          <t>정치적 논쟁만 가득한 게시글 내용.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광통신', '미국수주', '외인매수']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18450</v>
+        <v>18490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.65%</t>
+          <t>'-0.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.21</v>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
         <v>62</v>
       </c>
       <c r="G13" t="n">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H13" t="n">
         <v>10.85</v>
@@ -1622,7 +1622,7 @@
         <v>10.64</v>
       </c>
       <c r="O13" t="n">
-        <v>61791039755</v>
+        <v>62711286200</v>
       </c>
       <c r="P13" t="n">
         <v>40350</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1746000</v>
+        <v>1744000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.74%</t>
+          <t>'-0.85%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="G14" t="n">
-        <v>1701</v>
+        <v>1709</v>
       </c>
       <c r="H14" t="n">
         <v>50.2</v>
@@ -1714,7 +1714,7 @@
         <v>50.2</v>
       </c>
       <c r="O14" t="n">
-        <v>4071780314000</v>
+        <v>4145476089000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8370</v>
+        <v>11510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.18%</t>
+          <t>'-1.03%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.12</v>
+        <v>0.3</v>
       </c>
       <c r="E15" t="n">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F15" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G15" t="n">
-        <v>381</v>
+        <v>501</v>
       </c>
       <c r="H15" t="n">
-        <v>26.54</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8470</v>
+        <v>11630</v>
       </c>
       <c r="K15" t="n">
-        <v>8470</v>
+        <v>11700</v>
       </c>
       <c r="L15" t="n">
-        <v>8510</v>
+        <v>12760</v>
       </c>
       <c r="M15" t="n">
-        <v>8350</v>
+        <v>11500</v>
       </c>
       <c r="N15" t="n">
-        <v>26.66</v>
+        <v>8.4</v>
       </c>
       <c r="O15" t="n">
-        <v>16678589730</v>
+        <v>49848419180</v>
       </c>
       <c r="P15" t="n">
-        <v>17950</v>
+        <v>21150</v>
       </c>
       <c r="Q15" t="n">
-        <v>8120</v>
+        <v>8140</v>
       </c>
       <c r="R15" t="n">
-        <v>-236000</v>
+        <v>261000</v>
       </c>
       <c r="S15" t="n">
-        <v>-5000</v>
+        <v>5000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>4분기 전망 및 중국 경쟁 심화 우려. 무능한 경영진과 높은 부채 비중, 목표가 하향 조정 등 악재 지속.</t>
+          <t>주가 조작 및 루머 확산 의혹 제기, 경영진 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['부채', '경쟁력', '목표가']</t>
+          <t>['주가 조작', '헛소문']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3460</v>
+        <v>8380</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.70%</t>
+          <t>'-1.06%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.85</v>
+        <v>-0.12</v>
       </c>
       <c r="E16" t="n">
-        <v>102</v>
+        <v>161</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="G16" t="n">
-        <v>323</v>
+        <v>395</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26</v>
+        <v>26.54</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3520</v>
+        <v>8470</v>
       </c>
       <c r="K16" t="n">
-        <v>3730</v>
+        <v>8470</v>
       </c>
       <c r="L16" t="n">
-        <v>3750</v>
+        <v>8510</v>
       </c>
       <c r="M16" t="n">
-        <v>3420</v>
+        <v>8350</v>
       </c>
       <c r="N16" t="n">
-        <v>3.11</v>
+        <v>26.66</v>
       </c>
       <c r="O16" t="n">
-        <v>6202100725</v>
+        <v>17122178240</v>
       </c>
       <c r="P16" t="n">
-        <v>16110</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>2300</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-328000</v>
+        <v>-236000</v>
       </c>
       <c r="S16" t="n">
-        <v>-9000</v>
+        <v>-5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
+          <t>사업 전망 악화 및 경영진 무능 비판, 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,20 +1923,20 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['상장폐지', '폭락', '차익실현']</t>
+          <t>['전망 악화', '경영진 무능']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1958,13 +1958,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="H17" t="n">
         <v>3.71</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미 선다이오드와 방산용 AR 디스플레이 양산 협력. 신사업 본격화.</t>
+          <t>방산용 AR 디스플레이 신사업 본격화 소식에 대한 기대와 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AR디스플레이', '방산', '신사업']</t>
+          <t>['방산', 'AR 디스플레이']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,21 +2039,21 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13250</v>
+        <v>13240</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1.36</v>
       </c>
       <c r="E18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
         <v>96</v>
@@ -2082,7 +2082,7 @@
         <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>83906342190</v>
+        <v>84300483510</v>
       </c>
       <c r="P18" t="n">
         <v>25700</v>
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13670</v>
+        <v>3440</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.15%</t>
+          <t>'-2.27%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.01</v>
+        <v>-0.85</v>
       </c>
       <c r="E19" t="n">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="F19" t="n">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>400</v>
+        <v>323</v>
       </c>
       <c r="H19" t="n">
-        <v>0.01</v>
+        <v>2.26</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,60 +2159,60 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>13970</v>
+        <v>3520</v>
       </c>
       <c r="K19" t="n">
-        <v>13450</v>
+        <v>3730</v>
       </c>
       <c r="L19" t="n">
-        <v>13970</v>
+        <v>3750</v>
       </c>
       <c r="M19" t="n">
-        <v>13410</v>
+        <v>3420</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O19" t="n">
-        <v>16896844300</v>
+        <v>6462313390</v>
       </c>
       <c r="P19" t="n">
-        <v>36200</v>
+        <v>16110</v>
       </c>
       <c r="Q19" t="n">
-        <v>8920</v>
+        <v>2300</v>
       </c>
       <c r="R19" t="n">
-        <v>122000</v>
+        <v>-328000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-9000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>유가 변동성 및 지정학적 리스크에 따른 주가 등락. 외국인 매수세와 프로그램 매도 공존.</t>
+          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['유가', '지정학적 리스크', '외국인']</t>
+          <t>['상장폐지', '폭락', '차익실현']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10170</v>
+        <v>10210</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.77%</t>
+          <t>'-2.39%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.8</v>
       </c>
       <c r="E20" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F20" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H20" t="n">
         <v>18.42</v>
@@ -2266,7 +2266,7 @@
         <v>19.22</v>
       </c>
       <c r="O20" t="n">
-        <v>60538682415</v>
+        <v>61158656025</v>
       </c>
       <c r="P20" t="n">
         <v>22450</v>
@@ -2311,31 +2311,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4100</v>
+        <v>13630</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.03%</t>
+          <t>'-2.43%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="F21" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="G21" t="n">
-        <v>236</v>
+        <v>399</v>
       </c>
       <c r="H21" t="n">
-        <v>0.87</v>
+        <v>0.01</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,58 +2343,150 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4410</v>
+        <v>13970</v>
       </c>
       <c r="K21" t="n">
-        <v>4415</v>
+        <v>13450</v>
       </c>
       <c r="L21" t="n">
-        <v>4420</v>
+        <v>13970</v>
       </c>
       <c r="M21" t="n">
-        <v>4025</v>
+        <v>13410</v>
       </c>
       <c r="N21" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>53219087104</v>
+        <v>17304877050</v>
       </c>
       <c r="P21" t="n">
-        <v>8100</v>
+        <v>36200</v>
       </c>
       <c r="Q21" t="n">
-        <v>592</v>
+        <v>8920</v>
       </c>
       <c r="R21" t="n">
-        <v>-162000</v>
+        <v>122000</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>투기 과열 종목 지정으로 인한 주가 변동성 및 매도 압력 발생. 광통신 테마 내에서 대한광통신 대비 약세 언급.</t>
+          <t>유가 변동성 및 지정학적 리스크에 따른 주가 등락. 외국인 매수세와 프로그램 매도 공존.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['유가', '지정학적 리스크', '외국인']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>024060</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>빛과전자</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4110</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-6.80%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E22" t="n">
+        <v>83</v>
+      </c>
+      <c r="F22" t="n">
+        <v>62</v>
+      </c>
+      <c r="G22" t="n">
+        <v>243</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>4410</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4415</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4420</v>
+      </c>
+      <c r="M22" t="n">
+        <v>4025</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O22" t="n">
+        <v>53798051987</v>
+      </c>
+      <c r="P22" t="n">
+        <v>8100</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>592</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-162000</v>
+      </c>
+      <c r="S22" t="n">
         <v>0</v>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>투기 과열 종목 지정으로 인한 주가 변동성 및 매도 압력 발생. 광통신 테마 내에서 대한광통신 대비 약세 언급.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="inlineStr">
         <is>
           <t>['투기과열', '광통신', '주가변동']</t>
         </is>
       </c>
-      <c r="X21" t="n">
+      <c r="X22" t="n">
         <v>8</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>추적</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>069540</t>
         </is>

--- a/data/trending_integrated_20260917_15.xlsx
+++ b/data/trending_integrated_20260917_15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.91%</t>
+          <t>'+54.71%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.52</v>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H2" t="n">
         <v>1.39</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9730</v>
+        <v>8170</v>
       </c>
       <c r="K2" t="n">
-        <v>9700</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>12640</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>9350</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0.87</v>
       </c>
       <c r="O2" t="n">
-        <v>160218257075</v>
+        <v>160277000000</v>
       </c>
       <c r="P2" t="n">
-        <v>17040</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>5460</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>-12000</v>
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="F3" t="n">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="G3" t="n">
-        <v>1702</v>
+        <v>1721</v>
       </c>
       <c r="H3" t="n">
         <v>0.95</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>317849381964</v>
+        <v>318985170174</v>
       </c>
       <c r="P3" t="n">
         <v>6900</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1677</v>
+        <v>1686</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.04%</t>
+          <t>'+20.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F4" t="n">
         <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H4" t="n">
         <v>3.52</v>
@@ -794,7 +794,7 @@
         <v>3.57</v>
       </c>
       <c r="O4" t="n">
-        <v>55822092167</v>
+        <v>55960111499</v>
       </c>
       <c r="P4" t="n">
         <v>5140</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21500</v>
+        <v>21600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.84%</t>
+          <t>'+16.38%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>302120369270</v>
+        <v>303493459670</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3845</v>
+        <v>3855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.86%</t>
+          <t>'+10.14%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F6" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G6" t="n">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>100360006054</v>
+        <v>101148122254</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -1038,13 +1038,13 @@
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G7" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>88713161050</v>
+        <v>95175803050</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10460</v>
+        <v>10500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.91%</t>
+          <t>'+5.32%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>180898787585</v>
+        <v>181734566585</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1228,7 +1228,7 @@
         <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>63395792040</v>
+        <v>63816780100</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1314,13 +1314,13 @@
         <v>-0.1</v>
       </c>
       <c r="E10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F10" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G10" t="n">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>133569472700</v>
+        <v>141477256500</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16110</v>
+        <v>16130</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F11" t="n">
         <v>145</v>
       </c>
       <c r="G11" t="n">
-        <v>1439</v>
+        <v>1457</v>
       </c>
       <c r="H11" t="n">
         <v>4.88</v>
@@ -1438,7 +1438,7 @@
         <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>355661250360</v>
+        <v>356685779570</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>아이티센피엔에스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>253000</v>
+        <v>3485</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.20%</t>
+          <t>'+0.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>122</v>
       </c>
       <c r="F12" t="n">
-        <v>439</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
-        <v>1785</v>
+        <v>191</v>
       </c>
       <c r="H12" t="n">
-        <v>46.52</v>
+        <v>1.64</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>253500</v>
+        <v>3480</v>
       </c>
       <c r="K12" t="n">
-        <v>257000</v>
+        <v>3795</v>
       </c>
       <c r="L12" t="n">
-        <v>259000</v>
+        <v>3985</v>
       </c>
       <c r="M12" t="n">
-        <v>251500</v>
+        <v>2790</v>
       </c>
       <c r="N12" t="n">
-        <v>46.56</v>
+        <v>1.64</v>
       </c>
       <c r="O12" t="n">
-        <v>2490607149250</v>
+        <v>43541099716</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>5590</v>
       </c>
       <c r="Q12" t="n">
-        <v>77100</v>
+        <v>1211</v>
       </c>
       <c r="R12" t="n">
-        <v>-718000</v>
+        <v>-119000</v>
       </c>
       <c r="S12" t="n">
-        <v>-59000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 논쟁만 가득한 게시글 내용.</t>
+          <t>양자보안 관련 사업 확장 기대감 속 주가 변동성 관찰. 저평가 인식 및 매수/매도 전략.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['양자보안', '저평가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>232830</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18490</v>
+        <v>252500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.43%</t>
+          <t>'-0.39%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>62</v>
+        <v>437</v>
       </c>
       <c r="G13" t="n">
-        <v>401</v>
+        <v>1856</v>
       </c>
       <c r="H13" t="n">
-        <v>10.85</v>
+        <v>46.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18570</v>
+        <v>253500</v>
       </c>
       <c r="K13" t="n">
-        <v>18740</v>
+        <v>257000</v>
       </c>
       <c r="L13" t="n">
-        <v>18900</v>
+        <v>259000</v>
       </c>
       <c r="M13" t="n">
-        <v>18350</v>
+        <v>251500</v>
       </c>
       <c r="N13" t="n">
-        <v>10.64</v>
+        <v>46.56</v>
       </c>
       <c r="O13" t="n">
-        <v>62711286200</v>
+        <v>2767809476750</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>77100</v>
       </c>
       <c r="R13" t="n">
-        <v>-306000</v>
+        <v>-718000</v>
       </c>
       <c r="S13" t="n">
-        <v>-77000</v>
+        <v>-59000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
+          <t>정치적 성향에 따른 주가 언급 및 주가 조작 관련 의혹 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,51 +1647,51 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['대규모계약', 'LNG', '대차해지']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1744000</v>
+        <v>18490</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.85%</t>
+          <t>'-0.43%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>112</v>
       </c>
       <c r="F14" t="n">
-        <v>475</v>
+        <v>63</v>
       </c>
       <c r="G14" t="n">
-        <v>1709</v>
+        <v>408</v>
       </c>
       <c r="H14" t="n">
-        <v>50.2</v>
+        <v>10.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1759000</v>
+        <v>18570</v>
       </c>
       <c r="K14" t="n">
-        <v>1770000</v>
+        <v>18740</v>
       </c>
       <c r="L14" t="n">
-        <v>1785000</v>
+        <v>18900</v>
       </c>
       <c r="M14" t="n">
-        <v>1735000</v>
+        <v>18350</v>
       </c>
       <c r="N14" t="n">
-        <v>50.2</v>
+        <v>10.64</v>
       </c>
       <c r="O14" t="n">
-        <v>4145476089000</v>
+        <v>63588747640</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>333000</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>-242000</v>
+        <v>-306000</v>
       </c>
       <c r="S14" t="n">
-        <v>8000</v>
+        <v>-77000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>홀딩 및 실적 시즌 대비. 금리 인상 수혜 및 200돌파 기대.</t>
+          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적시즌', '금리인상', '주가상승']</t>
+          <t>['대규모계약', 'LNG', '대차해지']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11510</v>
+        <v>11580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.03%</t>
+          <t>'-0.43%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.3</v>
       </c>
       <c r="E15" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F15" t="n">
         <v>77</v>
       </c>
       <c r="G15" t="n">
-        <v>501</v>
+        <v>545</v>
       </c>
       <c r="H15" t="n">
         <v>8.699999999999999</v>
@@ -1806,7 +1806,7 @@
         <v>8.4</v>
       </c>
       <c r="O15" t="n">
-        <v>49848419180</v>
+        <v>50130948020</v>
       </c>
       <c r="P15" t="n">
         <v>21150</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>주가 조작 및 루머 확산 의혹 제기, 경영진 비판.</t>
+          <t>허위 사실 유포 및 악질적인 주가 조작 의혹 제기. 관련 기업 인수설 등 루머 기반 분석.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 조작', '헛소문']</t>
+          <t>['주가 조작', '공시']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8380</v>
+        <v>1745000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.06%</t>
+          <t>'-0.80%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>161</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>75</v>
+        <v>473</v>
       </c>
       <c r="G16" t="n">
-        <v>395</v>
+        <v>1731</v>
       </c>
       <c r="H16" t="n">
-        <v>26.54</v>
+        <v>50.2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8470</v>
+        <v>1759000</v>
       </c>
       <c r="K16" t="n">
-        <v>8470</v>
+        <v>1770000</v>
       </c>
       <c r="L16" t="n">
-        <v>8510</v>
+        <v>1785000</v>
       </c>
       <c r="M16" t="n">
-        <v>8350</v>
+        <v>1735000</v>
       </c>
       <c r="N16" t="n">
-        <v>26.66</v>
+        <v>50.2</v>
       </c>
       <c r="O16" t="n">
-        <v>17122178240</v>
+        <v>4511407824000</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R16" t="n">
-        <v>-236000</v>
+        <v>-242000</v>
       </c>
       <c r="S16" t="n">
-        <v>-5000</v>
+        <v>8000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>사업 전망 악화 및 경영진 무능 비판, 주가 하락세 지속.</t>
+          <t>홀딩 및 실적 시즌 대비. 금리 인상 수혜 및 200돌파 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['전망 악화', '경영진 무능']</t>
+          <t>['실적시즌', '금리인상', '주가상승']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55</v>
+        <v>8380</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.79%</t>
+          <t>'-1.06%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="E17" t="n">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
-        <v>287</v>
+        <v>398</v>
       </c>
       <c r="H17" t="n">
-        <v>3.71</v>
+        <v>26.54</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>56</v>
+        <v>8470</v>
       </c>
       <c r="K17" t="n">
-        <v>56</v>
+        <v>8470</v>
       </c>
       <c r="L17" t="n">
-        <v>90</v>
+        <v>8510</v>
       </c>
       <c r="M17" t="n">
-        <v>55</v>
+        <v>8350</v>
       </c>
       <c r="N17" t="n">
-        <v>3.71</v>
+        <v>26.66</v>
       </c>
       <c r="O17" t="n">
-        <v>634666899</v>
+        <v>18068950640</v>
       </c>
       <c r="P17" t="n">
-        <v>901</v>
+        <v>17950</v>
       </c>
       <c r="Q17" t="n">
-        <v>55</v>
+        <v>8120</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>-236000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>방산용 AR 디스플레이 신사업 본격화 소식에 대한 기대와 우려.</t>
+          <t>사업 전망 악화 및 경영진 무능 비판, 주가 하락세 지속.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['방산', 'AR 디스플레이']</t>
+          <t>['전망 악화', '경영진 무능']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>008290</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13240</v>
+        <v>13340</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'-1.40%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1.36</v>
       </c>
       <c r="E18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H18" t="n">
         <v>1.76</v>
@@ -2082,7 +2082,7 @@
         <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>84300483510</v>
+        <v>84661197110</v>
       </c>
       <c r="P18" t="n">
         <v>25700</v>
@@ -2127,70 +2127,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>이뮨온시아</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3440</v>
+        <v>10250</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.27%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.85</v>
+        <v>-0.8</v>
       </c>
       <c r="E19" t="n">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>323</v>
+        <v>148</v>
       </c>
       <c r="H19" t="n">
-        <v>2.26</v>
+        <v>18.42</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3520</v>
+        <v>10460</v>
       </c>
       <c r="K19" t="n">
-        <v>3730</v>
+        <v>10860</v>
       </c>
       <c r="L19" t="n">
-        <v>3750</v>
+        <v>11150</v>
       </c>
       <c r="M19" t="n">
-        <v>3420</v>
+        <v>10060</v>
       </c>
       <c r="N19" t="n">
-        <v>3.11</v>
+        <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>6462313390</v>
+        <v>61626353275</v>
       </c>
       <c r="P19" t="n">
-        <v>16110</v>
+        <v>22450</v>
       </c>
       <c r="Q19" t="n">
-        <v>2300</v>
+        <v>1760</v>
       </c>
       <c r="R19" t="n">
-        <v>-328000</v>
+        <v>-70000</v>
       </c>
       <c r="S19" t="n">
-        <v>-9000</v>
+        <v>-6000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
+          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['상장폐지', '폭락', '차익실현']</t>
+          <t>['주포', '시총', '횡보']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>424870</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>이뮨온시아</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10210</v>
+        <v>3445</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-2.13%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.8</v>
+        <v>-0.85</v>
       </c>
       <c r="E20" t="n">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>148</v>
+        <v>325</v>
       </c>
       <c r="H20" t="n">
-        <v>18.42</v>
+        <v>2.26</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10460</v>
+        <v>3520</v>
       </c>
       <c r="K20" t="n">
-        <v>10860</v>
+        <v>3730</v>
       </c>
       <c r="L20" t="n">
-        <v>11150</v>
+        <v>3750</v>
       </c>
       <c r="M20" t="n">
-        <v>10060</v>
+        <v>3420</v>
       </c>
       <c r="N20" t="n">
-        <v>19.22</v>
+        <v>3.11</v>
       </c>
       <c r="O20" t="n">
-        <v>61158656025</v>
+        <v>6603754755</v>
       </c>
       <c r="P20" t="n">
-        <v>22450</v>
+        <v>16110</v>
       </c>
       <c r="Q20" t="n">
-        <v>1760</v>
+        <v>2300</v>
       </c>
       <c r="R20" t="n">
-        <v>-70000</v>
+        <v>-328000</v>
       </c>
       <c r="S20" t="n">
-        <v>-6000</v>
+        <v>-9000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>대장주 언급 있으나, 주포 이탈 의혹 및 잡주 비판으로 투자 심리 부정적. 시총 증가로 인한 상승 여력 제한 언급.</t>
+          <t>회사의 상장 폐지 가능성이 제기되는 가운데, 주가 폭락 및 차익 실현 움직임이 두드러지며 투자자들의 좌절감이 나타남.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['주포', '시총', '횡보']</t>
+          <t>['상장폐지', '폭락', '차익실현']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>424870</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13630</v>
+        <v>13610</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-2.43%</t>
+          <t>'-2.58%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F21" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G21" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="H21" t="n">
         <v>0.01</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>17304877050</v>
+        <v>17652422010</v>
       </c>
       <c r="P21" t="n">
         <v>36200</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4110</v>
+        <v>4095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.80%</t>
+          <t>'-7.14%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.13</v>
       </c>
       <c r="E22" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F22" t="n">
         <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="H22" t="n">
         <v>0.87</v>
@@ -2450,7 +2450,7 @@
         <v>0.74</v>
       </c>
       <c r="O22" t="n">
-        <v>53798051987</v>
+        <v>54076036967</v>
       </c>
       <c r="P22" t="n">
         <v>8100</v>
@@ -2489,6 +2489,98 @@
       <c r="Z22" t="inlineStr">
         <is>
           <t>069540</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>43</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'-23.21%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>142</v>
+      </c>
+      <c r="F23" t="n">
+        <v>60</v>
+      </c>
+      <c r="G23" t="n">
+        <v>289</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>56</v>
+      </c>
+      <c r="K23" t="n">
+        <v>56</v>
+      </c>
+      <c r="L23" t="n">
+        <v>90</v>
+      </c>
+      <c r="M23" t="n">
+        <v>43</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="O23" t="n">
+        <v>689987689</v>
+      </c>
+      <c r="P23" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>43</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>방산용 AR 디스플레이 신사업 본격화 소식에 대한 기대와 우려.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>['방산', 'AR 디스플레이']</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>008290</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260917_15.xlsx
+++ b/data/trending_integrated_20260917_15.xlsx
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+54.71%</t>
+          <t>'+29.91%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.52</v>
       </c>
       <c r="E2" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H2" t="n">
         <v>1.39</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>8170</v>
+        <v>9730</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9700</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>12640</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>9350</v>
       </c>
       <c r="N2" t="n">
         <v>0.87</v>
       </c>
       <c r="O2" t="n">
-        <v>160277000000</v>
+        <v>160290772755</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>17040</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>5460</v>
       </c>
       <c r="R2" t="n">
         <v>-12000</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>삼성전기 MLCC 소재 공급 확대 논의 관련 뉴스 부각.</t>
+          <t>삼성전기 MLCC 소재 공급 확대 논의 뉴스 기반. 신규 진입 시 위험 경고. 투자 경고 종목 지정 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['MLCC', '소재']</t>
+          <t>['MLCC', '소재공급', '투자경고']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="F3" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="G3" t="n">
-        <v>1721</v>
+        <v>1788</v>
       </c>
       <c r="H3" t="n">
         <v>0.95</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="O3" t="n">
-        <v>318985170174</v>
+        <v>319002653394</v>
       </c>
       <c r="P3" t="n">
         <v>6900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>카카오 인수 및 소프트뱅크 투자 관련 루머로 급등 기대감 형성.</t>
+          <t>카카오 인수 및 소프트뱅크 투자 관련 기대감. 높은 거래량과 급등 가능성 언급. 텐버거(10배 상승) 가능성 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['카카오 인수', '손정의']</t>
+          <t>['카카오인수', '소프트뱅크', '텐버거']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="H4" t="n">
         <v>3.52</v>
@@ -794,7 +794,7 @@
         <v>3.57</v>
       </c>
       <c r="O4" t="n">
-        <v>55960111499</v>
+        <v>55964785091</v>
       </c>
       <c r="P4" t="n">
         <v>5140</v>
@@ -854,13 +854,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F5" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H5" t="n">
         <v>2.54</v>
@@ -886,7 +886,7 @@
         <v>1.92</v>
       </c>
       <c r="O5" t="n">
-        <v>303493459670</v>
+        <v>303553853270</v>
       </c>
       <c r="P5" t="n">
         <v>59600</v>
@@ -952,7 +952,7 @@
         <v>76</v>
       </c>
       <c r="G6" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H6" t="n">
         <v>8.01</v>
@@ -978,7 +978,7 @@
         <v>8.06</v>
       </c>
       <c r="O6" t="n">
-        <v>101148122254</v>
+        <v>101184817999</v>
       </c>
       <c r="P6" t="n">
         <v>19950</v>
@@ -1038,13 +1038,13 @@
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F7" t="n">
         <v>77</v>
       </c>
       <c r="G7" t="n">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="H7" t="n">
         <v>28.36</v>
@@ -1070,7 +1070,7 @@
         <v>28.51</v>
       </c>
       <c r="O7" t="n">
-        <v>95175803050</v>
+        <v>95184446050</v>
       </c>
       <c r="P7" t="n">
         <v>35350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>신규 수주 기대감 속 개인 투자자들의 매수세 집중.</t>
+          <t>장기 투자 및 추가 매수 관점 제시. 금리 인상 영향 언급. 공매도 세력에 대한 경계와 추세 전환 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신규 수주', '추세 전환']</t>
+          <t>['장기투자', '금리인상', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1136,7 +1136,7 @@
         <v>89</v>
       </c>
       <c r="G8" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="H8" t="n">
         <v>1.25</v>
@@ -1162,7 +1162,7 @@
         <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>181734566585</v>
+        <v>181758212585</v>
       </c>
       <c r="P8" t="n">
         <v>15960</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>낙태약 및 탈모 치료제 관련 기대감. 예상 매출 1조 이상 언급.</t>
+          <t>낙태약 도입 및 탈모 치료 수혜주 언급. 예상 매출 1조 이상 전망. 외국인 및 프로그램 매도세 유출 관찰.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['낙태약', '탈모치료', '매출']</t>
+          <t>['낙태약', '탈모치료', '외국인']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1228,7 +1228,7 @@
         <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="H9" t="n">
         <v>4.99</v>
@@ -1254,7 +1254,7 @@
         <v>5.12</v>
       </c>
       <c r="O9" t="n">
-        <v>63816780100</v>
+        <v>63827564070</v>
       </c>
       <c r="P9" t="n">
         <v>30200</v>
@@ -1320,7 +1320,7 @@
         <v>131</v>
       </c>
       <c r="G10" t="n">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="H10" t="n">
         <v>23.27</v>
@@ -1346,7 +1346,7 @@
         <v>23.37</v>
       </c>
       <c r="O10" t="n">
-        <v>141477256500</v>
+        <v>141485711100</v>
       </c>
       <c r="P10" t="n">
         <v>139200</v>
@@ -1406,13 +1406,13 @@
         <v>2.93</v>
       </c>
       <c r="E11" t="n">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="F11" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G11" t="n">
-        <v>1457</v>
+        <v>1476</v>
       </c>
       <c r="H11" t="n">
         <v>4.88</v>
@@ -1438,7 +1438,7 @@
         <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>356685779570</v>
+        <v>356740040890</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1498,13 +1498,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H12" t="n">
         <v>1.64</v>
@@ -1530,7 +1530,7 @@
         <v>1.64</v>
       </c>
       <c r="O12" t="n">
-        <v>43541099716</v>
+        <v>43542099911</v>
       </c>
       <c r="P12" t="n">
         <v>5590</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>양자보안 관련 사업 확장 기대감 속 주가 변동성 관찰. 저평가 인식 및 매수/매도 전략.</t>
+          <t>양자보안 의무화 관련 고객사 언급. 주가 저평가 및 단기 수익 실현 후 매도. 투자 경고 및 관리 종목 지정 관련 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['양자보안', '저평가']</t>
+          <t>['양자보안', '저평가', '투자경고']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="G13" t="n">
-        <v>1856</v>
+        <v>1880</v>
       </c>
       <c r="H13" t="n">
         <v>46.52</v>
@@ -1622,7 +1622,7 @@
         <v>46.56</v>
       </c>
       <c r="O13" t="n">
-        <v>2767809476750</v>
+        <v>2767845079250</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 성향에 따른 주가 언급 및 주가 조작 관련 의혹 제기.</t>
+          <t>정치적 성향 게시 자제 요청. 주가 하락에 대한 감성적 언급. 프로그램 매도 물량 출회 및 여야 정치 관련 논쟁.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치', '프로그램매도', '주가하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,11 +1667,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>파미셀</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18490</v>
+        <v>11580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>0.3</v>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="F14" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="G14" t="n">
-        <v>408</v>
+        <v>581</v>
       </c>
       <c r="H14" t="n">
-        <v>10.85</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,71 +1699,71 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18570</v>
+        <v>11630</v>
       </c>
       <c r="K14" t="n">
-        <v>18740</v>
+        <v>11700</v>
       </c>
       <c r="L14" t="n">
-        <v>18900</v>
+        <v>12760</v>
       </c>
       <c r="M14" t="n">
-        <v>18350</v>
+        <v>11500</v>
       </c>
       <c r="N14" t="n">
-        <v>10.64</v>
+        <v>8.4</v>
       </c>
       <c r="O14" t="n">
-        <v>63588747640</v>
+        <v>50141601620</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>21150</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>8140</v>
       </c>
       <c r="R14" t="n">
-        <v>-306000</v>
+        <v>261000</v>
       </c>
       <c r="S14" t="n">
-        <v>-77000</v>
+        <v>-5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
+          <t>삼성 인수 등 루머에 대한 비판. 회사의 악질적인 운영에 대한 불만 표출. 목표 주가와 현재 주가 간 괴리 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['대규모계약', 'LNG', '대차해지']</t>
+          <t>['루머', '악질', '목표주가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005690</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>파미셀</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11580</v>
+        <v>18490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1771,19 +1771,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="E15" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="F15" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="G15" t="n">
-        <v>545</v>
+        <v>427</v>
       </c>
       <c r="H15" t="n">
-        <v>8.699999999999999</v>
+        <v>10.85</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,60 +1791,60 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>11630</v>
+        <v>18570</v>
       </c>
       <c r="K15" t="n">
-        <v>11700</v>
+        <v>18740</v>
       </c>
       <c r="L15" t="n">
-        <v>12760</v>
+        <v>18900</v>
       </c>
       <c r="M15" t="n">
-        <v>11500</v>
+        <v>18350</v>
       </c>
       <c r="N15" t="n">
-        <v>8.4</v>
+        <v>10.64</v>
       </c>
       <c r="O15" t="n">
-        <v>50130948020</v>
+        <v>63621493430</v>
       </c>
       <c r="P15" t="n">
-        <v>21150</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>8140</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>261000</v>
+        <v>-306000</v>
       </c>
       <c r="S15" t="n">
-        <v>5000</v>
+        <v>-77000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>허위 사실 유포 및 악질적인 주가 조작 의혹 제기. 관련 기업 인수설 등 루머 기반 분석.</t>
+          <t>대규모 계약 체결 및 LNG 협의 기대감과 함께, 대차 해지 운동 참여 독려 및 공매도 세력에 대한 강경한 입장이 나타남.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가 조작', '공시']</t>
+          <t>['대규모계약', 'LNG', '대차해지']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005690</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
         <v>473</v>
       </c>
       <c r="G16" t="n">
-        <v>1731</v>
+        <v>1758</v>
       </c>
       <c r="H16" t="n">
         <v>50.2</v>
@@ -1898,7 +1898,7 @@
         <v>50.2</v>
       </c>
       <c r="O16" t="n">
-        <v>4511407824000</v>
+        <v>4511454939000</v>
       </c>
       <c r="P16" t="n">
         <v>2987000</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>홀딩 및 실적 시즌 대비. 금리 인상 수혜 및 200돌파 기대.</t>
+          <t>장기 보유 의견 제시. 실적 시즌 도래 및 금리 인상 수혜 기대. 외국인 현물 매도 및 선물 매수 관찰.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적시즌', '금리인상', '주가상승']</t>
+          <t>['실적시즌', '금리인상', '외국인']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>-0.12</v>
       </c>
       <c r="E17" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F17" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17" t="n">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="H17" t="n">
         <v>26.54</v>
@@ -1990,7 +1990,7 @@
         <v>26.66</v>
       </c>
       <c r="O17" t="n">
-        <v>18068950640</v>
+        <v>18073676960</v>
       </c>
       <c r="P17" t="n">
         <v>17950</v>
@@ -2082,7 +2082,7 @@
         <v>0.4</v>
       </c>
       <c r="O18" t="n">
-        <v>84661197110</v>
+        <v>84709354510</v>
       </c>
       <c r="P18" t="n">
         <v>25700</v>
@@ -2145,10 +2145,10 @@
         <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H19" t="n">
         <v>18.42</v>
@@ -2174,7 +2174,7 @@
         <v>19.22</v>
       </c>
       <c r="O19" t="n">
-        <v>61626353275</v>
+        <v>61663745275</v>
       </c>
       <c r="P19" t="n">
         <v>22450</v>
@@ -2234,13 +2234,13 @@
         <v>-0.85</v>
       </c>
       <c r="E20" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="H20" t="n">
         <v>2.26</v>
@@ -2326,13 +2326,13 @@
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F21" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" t="n">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="H21" t="n">
         <v>0.01</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>17652422010</v>
+        <v>17670496090</v>
       </c>
       <c r="P21" t="n">
         <v>36200</v>
@@ -2418,13 +2418,13 @@
         <v>0.13</v>
       </c>
       <c r="E22" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F22" t="n">
         <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H22" t="n">
         <v>0.87</v>
@@ -2450,7 +2450,7 @@
         <v>0.74</v>
       </c>
       <c r="O22" t="n">
-        <v>54076036967</v>
+        <v>54162601172</v>
       </c>
       <c r="P22" t="n">
         <v>8100</v>
@@ -2510,13 +2510,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="H23" t="n">
         <v>3.71</v>
@@ -2542,7 +2542,7 @@
         <v>3.71</v>
       </c>
       <c r="O23" t="n">
-        <v>689987689</v>
+        <v>696433991</v>
       </c>
       <c r="P23" t="n">
         <v>901</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>방산용 AR 디스플레이 신사업 본격화 소식에 대한 기대와 우려.</t>
+          <t>회사 부채 및 주가 하락에 대한 우려. 개미 투자자들의 움직임에 대한 관찰. 법적 대응 및 희망 고문 비판.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['방산', 'AR 디스플레이']</t>
+          <t>['부채', '개미', '희망고문']</t>
         </is>
       </c>
       <c r="X23" t="n">
